--- a/data/trans_bre/P36BPD07_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P36BPD07_R-Estudios-trans_bre.xlsx
@@ -578,7 +578,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>5,0</t>
+          <t>3,01</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>4,05%</t>
         </is>
       </c>
     </row>
@@ -601,22 +601,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,32; 5,68</t>
+          <t>0,13; 5,21</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,64; 9,23</t>
+          <t>-1,17; 7,12</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,28; 6,33</t>
+          <t>0,15; 5,8</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,83; 13,33</t>
+          <t>-1,58; 9,94</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5,45</t>
+          <t>5,88</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>8,71%</t>
         </is>
       </c>
     </row>
@@ -661,22 +661,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 3,95</t>
+          <t>-0,76; 3,91</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 11,9</t>
+          <t>3,03; 8,84</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 4,94</t>
+          <t>-0,9; 4,9</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,45; 16,79</t>
+          <t>4,36; 13,41</t>
         </is>
       </c>
     </row>
@@ -698,7 +698,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>3,83</t>
+          <t>2,26</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>2,78%</t>
         </is>
       </c>
     </row>
@@ -721,22 +721,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 4,63</t>
+          <t>-2,91; 4,49</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 9,41</t>
+          <t>-2,06; 6,4</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,59; 5,36</t>
+          <t>-3,24; 5,23</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 12,29</t>
+          <t>-2,52; 8,21</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>5,07</t>
+          <t>4,84</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,78%</t>
         </is>
       </c>
     </row>
@@ -781,22 +781,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,65; 4,04</t>
+          <t>0,75; 4,04</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 9,28</t>
+          <t>2,86; 6,98</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,76; 4,84</t>
+          <t>0,88; 4,84</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 12,83</t>
+          <t>3,96; 9,93</t>
         </is>
       </c>
     </row>
